--- a/output/pdf_financials_xlsx/IVQ.U.xlsx
+++ b/output/pdf_financials_xlsx/IVQ.U.xlsx
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>34.133</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>19.369</v>
@@ -1319,10 +1319,10 @@
         <v>10.745</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>18.157</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>39.334</v>
       </c>
     </row>
     <row r="35">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>34.133</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>19.369</v>
@@ -1369,10 +1369,10 @@
         <v>10.745</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>18.157</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>39.334</v>
       </c>
     </row>
     <row r="37">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>58.1</v>
+        <v>23.967</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>49.952</v>
@@ -1669,10 +1669,10 @@
         <v>27.33</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>345.205</v>
+        <v>327.048</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>40.804</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="49">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/IVQ.U.xlsx
+++ b/output/pdf_financials_xlsx/IVQ.U.xlsx
@@ -856,13 +856,13 @@
         <v>-5.712</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-5.673</v>
+        <v>-1.127</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-8.818</v>
+        <v>-0.312</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.196</v>
+        <v>-1.605</v>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
@@ -954,16 +954,16 @@
         <v>-184.004</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-5.712</v>
+        <v>-6.523</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-6.8</v>
+        <v>-42.01</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-99.23999999999999</v>
+        <v>-90.11</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-36.137</v>
+        <v>-32.81</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-5.712</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-6.8</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.409</v>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>48.569</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>22.152</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>16.516</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>15.584</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>13.256</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
@@ -1192,19 +1192,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-190.948</v>
+        <v>-142.379</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.523</v>
+        <v>15.629</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-43.137</v>
+        <v>-26.621</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-90.422</v>
+        <v>-74.83799999999999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-37.333</v>
+        <v>-24.077</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1219,19 +1219,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-87.83781918881995</v>
+        <v>-65.49563681360891</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-3.325567049202894</v>
+        <v>7.968003589144875</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-21.7825131921125</v>
+        <v>-13.44257328250057</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-46.89232428732193</v>
+        <v>-38.81055235467694</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-22.23936521930791</v>
+        <v>-14.34273153470861</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -1252,13 +1252,13 @@
         <v>-87.56707036639582</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-13.1511231657278</v>
+        <v>-2.612606347219324</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-9.752051491893566</v>
+        <v>-0.345048771316715</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-3.203600032143144</v>
+        <v>-4.299145528085072</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -2965,19 +2965,19 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>48.569</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>22.152</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>16.516</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>15.584</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>13.256</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -3271,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>13.225</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.148</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.783</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.163</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -10690,7 +10690,11 @@
           <t>Depreciation and amortization expense (note 7)</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -11086,7 +11090,11 @@
           <t>Deferred income tax recovery (note 25)</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -11672,7 +11680,11 @@
           <t>Payment for repurchase of common shares (note 17)</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -11808,7 +11820,11 @@
           <t>Proceeds from dispositions of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -12206,7 +12222,11 @@
           <t>Depreciation and amortization expense (note 7)</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -12598,7 +12618,11 @@
           <t>Deferred income tax recovery (note 25)</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -13244,7 +13268,11 @@
           <t>Payment for repurchase of common shares (note 17)</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -13508,7 +13536,11 @@
           <t>Proceeds from dispositions of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -14780,7 +14812,11 @@
           <t>Payment for repurchase of common shares</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -15224,7 +15260,11 @@
           <t>Depreciation and amortization expense (note 6)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E258" s="5" t="n">
         <v>48.569</v>
       </c>
@@ -15936,7 +15976,11 @@
           <t>Payment for repurchase of common shares</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E274" s="5" t="n">
         <v>-0.148</v>
       </c>
@@ -17780,7 +17824,11 @@
           <t>Deferred income tax recovery (note 24) —</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -17826,7 +17874,11 @@
           <t>Net loss from continuing operations $ (30,556) $</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -17872,7 +17924,11 @@
           <t>Net loss from discontinued operations (note 15) (934)</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -18530,7 +18586,11 @@
           <t>Depreciation and amortization expense (note 7)</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -19154,7 +19214,11 @@
           <t>Deferred income tax recovery (note 25)</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -19196,7 +19260,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -19236,7 +19304,11 @@
           <t>Net loss from discontinued operations (note 16)</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -20028,7 +20100,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -20484,7 +20556,11 @@
           <t>Depreciation and amortization expense (note 6)</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E376" s="5" t="n">
         <v>48.569</v>
       </c>
